--- a/ComputationTimePerFile.xlsx
+++ b/ComputationTimePerFile.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10511"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10905"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ramon/Library/CloudStorage/Dropbox/DDLV/LSPS/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ramon/Documents/GitHub/LSPS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{314ACE15-66C3-9C4F-9D31-A84DCD280C65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F31B239E-6F8C-8247-AAA6-70C089ACF654}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="840" yWindow="1000" windowWidth="28040" windowHeight="17440" xr2:uid="{6A15F2D7-94BC-F647-8DE7-DD7F3A5D979B}"/>
+    <workbookView xWindow="840" yWindow="1000" windowWidth="25240" windowHeight="17440" xr2:uid="{6A15F2D7-94BC-F647-8DE7-DD7F3A5D979B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,10 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="103">
-  <si>
-    <t>Size</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="117">
   <si>
     <t>WeightFunctionsMC.py</t>
   </si>
@@ -56,12 +53,6 @@
     <t>Cores</t>
   </si>
   <si>
-    <t>Power</t>
-  </si>
-  <si>
-    <t>NS5_L_C20</t>
-  </si>
-  <si>
     <t>02SizeMain_Plot_Fig.py</t>
   </si>
   <si>
@@ -80,9 +71,6 @@
     <t>02PowerMain_NS5_L_C20_Plot.py</t>
   </si>
   <si>
-    <t>LP_L_C20</t>
-  </si>
-  <si>
     <t>01PowerMain_LP_L_C20_Calc.py</t>
   </si>
   <si>
@@ -107,15 +95,6 @@
     <t>01_A_PowerMain_NS5_C_C200_Sim.py</t>
   </si>
   <si>
-    <t>ReadMe.txt</t>
-  </si>
-  <si>
-    <t>NS5_L_C200</t>
-  </si>
-  <si>
-    <t>LocalDiv</t>
-  </si>
-  <si>
     <t>DivergencesBasis.py</t>
   </si>
   <si>
@@ -134,12 +113,6 @@
     <t>02DivergencesMain_Plot.py</t>
   </si>
   <si>
-    <t>NS5_C_C200</t>
-  </si>
-  <si>
-    <t>Climate Application</t>
-  </si>
-  <si>
     <t>01DensityForecasts</t>
   </si>
   <si>
@@ -173,12 +146,6 @@
     <t>ScoreBasis.py</t>
   </si>
   <si>
-    <t>01_random_walk_oos_y.R</t>
-  </si>
-  <si>
-    <t>02A_call_model_ar.R</t>
-  </si>
-  <si>
     <t>Functions/functions.R</t>
   </si>
   <si>
@@ -188,24 +155,6 @@
     <t>&lt; 00:01:00</t>
   </si>
   <si>
-    <t>02B_call_model_bagging.R</t>
-  </si>
-  <si>
-    <t>02C_call_model_csr.R</t>
-  </si>
-  <si>
-    <t>02D_call_model_lasso.R</t>
-  </si>
-  <si>
-    <t>02E_call_model_rf.R</t>
-  </si>
-  <si>
-    <t>02F_call_model_rw.R</t>
-  </si>
-  <si>
-    <t>Inflation Application</t>
-  </si>
-  <si>
     <t>InflationScoreCalcMain_C_h6.py</t>
   </si>
   <si>
@@ -233,9 +182,6 @@
     <t>RiskManBasisMV.py</t>
   </si>
   <si>
-    <t>Multivariate Risk Management</t>
-  </si>
-  <si>
     <t>Weightfunctions.py</t>
   </si>
   <si>
@@ -251,9 +197,6 @@
     <t>RiskManMainBivariateLogProd3</t>
   </si>
   <si>
-    <t>Univariate Risk Management</t>
-  </si>
-  <si>
     <t>RiskManMain.py</t>
   </si>
   <si>
@@ -263,9 +206,6 @@
     <t>03MCS</t>
   </si>
   <si>
-    <t>Readme.txt</t>
-  </si>
-  <si>
     <t>MCSTables_ClimateCenter.R</t>
   </si>
   <si>
@@ -345,6 +285,108 @@
   </si>
   <si>
     <t>Files without a listed computation time are helper functions or data</t>
+  </si>
+  <si>
+    <t>06_MITCHELL_AND_WEALE_Example_6</t>
+  </si>
+  <si>
+    <t>01_RISK_MANAGEMENT_Table_2_Appendix_I</t>
+  </si>
+  <si>
+    <t>02_MULTIVARIATE_RISK_MANAGEMENT_Table_2_Appendix_I</t>
+  </si>
+  <si>
+    <t>03_INFLATION_Table_2_Appendix_I</t>
+  </si>
+  <si>
+    <t>04_CLIMATE_Table_2_Appendix_I</t>
+  </si>
+  <si>
+    <t>05_MONTE_CARLO_Appendix_G</t>
+  </si>
+  <si>
+    <t>Example6.py</t>
+  </si>
+  <si>
+    <t>ReadMe_MITCHELL_AND_WEALE.txt</t>
+  </si>
+  <si>
+    <t>ReadMe_RISK_MANAGEMENT.txt</t>
+  </si>
+  <si>
+    <t>ReadMe_MULTIVARIATE_RISK_MANAGEMENT.txt</t>
+  </si>
+  <si>
+    <t>ReadMe_INFLATION.txt</t>
+  </si>
+  <si>
+    <t>ReadMe_CLIMATE.txt</t>
+  </si>
+  <si>
+    <t>ReadMe_FIG_G1.txt</t>
+  </si>
+  <si>
+    <t>ReadMe_FIG_G2.txt</t>
+  </si>
+  <si>
+    <t>FIG_G1_Size</t>
+  </si>
+  <si>
+    <t>FIG_G2_RejRates_NS5_L_C20</t>
+  </si>
+  <si>
+    <t>FIG_G3_LocalDiv_NS5_L_C20</t>
+  </si>
+  <si>
+    <t>ReadMe_FIG_G3.txt</t>
+  </si>
+  <si>
+    <t>ReadMe_FIG_G4.txt</t>
+  </si>
+  <si>
+    <t>ReadMe_FIG_G6.txt</t>
+  </si>
+  <si>
+    <t>FIG_G6_RejRates_LP_L_C20</t>
+  </si>
+  <si>
+    <t>ReadMe_FIG_G5.txt</t>
+  </si>
+  <si>
+    <t>FIG_G5_LocalDiv_NS5_C_C200</t>
+  </si>
+  <si>
+    <t>ReadMe_FIG_G7</t>
+  </si>
+  <si>
+    <t>FIG_G7_LocalDiv_LP_L_C20</t>
+  </si>
+  <si>
+    <t>01_get_fred_data.R</t>
+  </si>
+  <si>
+    <t>02_random_walk_oos_y.R</t>
+  </si>
+  <si>
+    <t>03A_call_model_ar.R</t>
+  </si>
+  <si>
+    <t>03B_call_model_bagging.R</t>
+  </si>
+  <si>
+    <t>03C_call_model_csr.R</t>
+  </si>
+  <si>
+    <t>03D_call_model_lasso.R</t>
+  </si>
+  <si>
+    <t>03E_call_model_rf.R</t>
+  </si>
+  <si>
+    <t>03F_call_model_rw.R</t>
+  </si>
+  <si>
+    <t>FIG_G4_RejRates_NS5_C_C200</t>
   </si>
 </sst>
 </file>
@@ -420,7 +462,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -439,6 +481,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -452,7 +500,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -485,6 +533,8 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -819,1048 +869,1179 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8EC44D52-E2DD-5A4B-80B5-8ADBC87B542B}">
-  <dimension ref="A1:F151"/>
+  <dimension ref="A1:F169"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="38.6640625" customWidth="1"/>
+    <col min="1" max="1" width="51.6640625" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" style="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="12" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" s="12" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="16" t="s">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="B1" s="13"/>
     </row>
-    <row r="2" spans="1:5" s="12" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" s="12" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="17" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="B2" s="15"/>
       <c r="C2" s="14"/>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B4" s="7" t="s">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E4" s="1"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B5" s="8"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="8">
-        <v>7.7118055555555551E-2</v>
-      </c>
-      <c r="C6">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>53</v>
+      </c>
+      <c r="B8" s="8">
+        <v>2.8009259259259259E-3</v>
+      </c>
+      <c r="C8">
         <v>192</v>
       </c>
-      <c r="D6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="8"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+        <v>68</v>
+      </c>
+      <c r="B9" s="8">
+        <v>2.9513888888888888E-3</v>
+      </c>
+      <c r="C9">
+        <v>192</v>
+      </c>
+      <c r="D9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+        <v>69</v>
+      </c>
+      <c r="B10" s="8">
+        <v>3.3680555555555556E-3</v>
+      </c>
+      <c r="C10">
+        <v>192</v>
+      </c>
+      <c r="D10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A14" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A15" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A14" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>70</v>
+      </c>
+      <c r="B15" s="8">
+        <v>1.4351851851851852E-2</v>
+      </c>
+      <c r="C15">
+        <v>192</v>
+      </c>
+      <c r="D15" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>12</v>
+        <v>71</v>
       </c>
       <c r="B16" s="8">
-        <v>0.15875</v>
+        <v>1.494212962962963E-2</v>
       </c>
       <c r="C16">
-        <v>256</v>
+        <v>192</v>
       </c>
       <c r="D16" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+        <v>72</v>
+      </c>
+      <c r="B17" s="8">
+        <v>1.3530092592592592E-2</v>
+      </c>
+      <c r="C17">
+        <v>192</v>
+      </c>
+      <c r="D17" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A24" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>22</v>
-      </c>
-      <c r="B25" s="8">
-        <v>3.1250000000000002E-3</v>
-      </c>
-      <c r="C25">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A22" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="F22" s="6"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>73</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
+      <c r="D23" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>74</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="C24">
+        <v>1</v>
+      </c>
+      <c r="D24" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B26" s="9"/>
+      <c r="C26"/>
+      <c r="D26"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A27" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B27" s="10"/>
+      <c r="C27" s="4"/>
+      <c r="D27" s="4"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A28" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>46</v>
+      </c>
+      <c r="B29" s="8">
+        <v>7.2453703703703708E-3</v>
+      </c>
+      <c r="C29">
         <v>192</v>
       </c>
-      <c r="D25" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
-        <v>21</v>
-      </c>
-      <c r="B26" s="8">
-        <v>5.3969907407407404E-2</v>
-      </c>
-      <c r="C26">
-        <v>192</v>
-      </c>
-      <c r="D26" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A30" s="2" t="s">
+      <c r="D29" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>15</v>
-      </c>
-      <c r="B31" s="8">
-        <v>0.17752314814814815</v>
-      </c>
-      <c r="C31">
-        <v>256</v>
-      </c>
-      <c r="D31" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A35" s="3" t="s">
-        <v>25</v>
+      <c r="A35" s="2" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A36" s="2" t="s">
-        <v>7</v>
+      <c r="A36" t="s">
+        <v>51</v>
+      </c>
+      <c r="B36" s="8">
+        <v>0.24607638888888889</v>
+      </c>
+      <c r="C36">
+        <v>1152</v>
+      </c>
+      <c r="D36" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>26</v>
+        <v>52</v>
+      </c>
+      <c r="B37" s="8">
+        <v>0.12196759259259259</v>
+      </c>
+      <c r="C37">
+        <f>6*192</f>
+        <v>1152</v>
+      </c>
+      <c r="D37" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>30</v>
+        <v>49</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>27</v>
-      </c>
-      <c r="B40" s="8">
-        <v>4.6296296296296294E-3</v>
-      </c>
-      <c r="C40">
-        <v>192</v>
-      </c>
-      <c r="D40" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A41" t="s">
-        <v>28</v>
-      </c>
-      <c r="B41" s="8">
-        <v>4.4791666666666669E-3</v>
-      </c>
-      <c r="C41">
-        <v>192</v>
-      </c>
-      <c r="D41" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A42" t="s">
-        <v>31</v>
+      <c r="A42" s="2" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A45" s="2" t="s">
-        <v>14</v>
+        <v>66</v>
+      </c>
+      <c r="B43" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="C43">
+        <v>1</v>
+      </c>
+      <c r="D43" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>67</v>
+      </c>
+      <c r="B44" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="C44">
+        <v>1</v>
+      </c>
+      <c r="D44" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A46" t="s">
-        <v>27</v>
-      </c>
-      <c r="B46" s="8">
-        <v>5.4282407407407404E-3</v>
-      </c>
-      <c r="C46">
-        <v>192</v>
-      </c>
-      <c r="D46" t="s">
-        <v>18</v>
+      <c r="A46" s="3" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A47" t="s">
-        <v>28</v>
-      </c>
-      <c r="B47" s="8">
-        <v>5.4166666666666669E-3</v>
-      </c>
-      <c r="C47">
-        <v>192</v>
-      </c>
-      <c r="D47" t="s">
-        <v>18</v>
+      <c r="A47" s="5" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A48" t="s">
-        <v>31</v>
+      <c r="A48" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A49" t="s">
-        <v>23</v>
+      <c r="A49" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="B49" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C49">
+        <v>1</v>
+      </c>
+      <c r="D49" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
+        <v>109</v>
+      </c>
+      <c r="B50" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C50">
+        <v>1</v>
+      </c>
+      <c r="D50" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A51" s="2" t="s">
-        <v>32</v>
+      <c r="A51" t="s">
+        <v>110</v>
+      </c>
+      <c r="B51" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C51">
+        <v>1</v>
+      </c>
+      <c r="D51" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>27</v>
+        <v>111</v>
       </c>
       <c r="B52" s="8">
-        <v>5.4398148148148149E-3</v>
+        <v>5.5555555555555558E-3</v>
       </c>
       <c r="C52">
-        <v>192</v>
+        <v>1</v>
       </c>
       <c r="D52" t="s">
-        <v>18</v>
+        <v>76</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>28</v>
-      </c>
-      <c r="B53" s="8">
-        <v>5.4629629629629629E-3</v>
+        <v>112</v>
+      </c>
+      <c r="B53" s="11">
+        <v>6.2500000000000003E-3</v>
       </c>
       <c r="C53">
-        <v>192</v>
+        <v>1</v>
       </c>
       <c r="D53" t="s">
-        <v>18</v>
+        <v>76</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>31</v>
+        <v>113</v>
+      </c>
+      <c r="B54" s="8">
+        <v>2.7777777777777779E-3</v>
+      </c>
+      <c r="C54">
+        <v>1</v>
+      </c>
+      <c r="D54" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>23</v>
+        <v>114</v>
+      </c>
+      <c r="B55" s="8">
+        <v>7.1527777777777773E-2</v>
+      </c>
+      <c r="C55">
+        <v>1</v>
+      </c>
+      <c r="D55" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
+        <v>115</v>
+      </c>
+      <c r="B56" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C56">
+        <v>1</v>
+      </c>
+      <c r="D56" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A57" s="3" t="s">
-        <v>71</v>
+      <c r="A57" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A58" s="5" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A59" s="2" t="s">
-        <v>34</v>
+      <c r="A58" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A60" t="s">
-        <v>72</v>
-      </c>
-      <c r="B60" s="8">
-        <v>2.8009259259259259E-3</v>
-      </c>
-      <c r="C60">
-        <v>192</v>
-      </c>
-      <c r="D60" t="s">
-        <v>18</v>
+      <c r="A60" s="2" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>88</v>
+        <v>39</v>
       </c>
       <c r="B61" s="8">
-        <v>2.9513888888888888E-3</v>
+        <v>6.134259259259259E-4</v>
       </c>
       <c r="C61">
-        <v>192</v>
+        <v>128</v>
       </c>
       <c r="D61" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>89</v>
+        <v>40</v>
       </c>
       <c r="B62" s="8">
-        <v>3.3680555555555556E-3</v>
+        <v>1.0300925925925926E-3</v>
       </c>
       <c r="C62">
-        <v>192</v>
+        <v>128</v>
       </c>
       <c r="D62" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>60</v>
       </c>
+      <c r="B63" s="8">
+        <v>1.3773148148148147E-3</v>
+      </c>
+      <c r="C63">
+        <v>128</v>
+      </c>
+      <c r="D63" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A66" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
+        <v>61</v>
+      </c>
+      <c r="B64" s="8">
+        <v>1.5509259259259259E-3</v>
+      </c>
+      <c r="C64">
+        <v>128</v>
+      </c>
+      <c r="D64" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A65" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A66" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>90</v>
-      </c>
-      <c r="B67" s="8">
-        <v>1.4351851851851852E-2</v>
-      </c>
-      <c r="C67">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A69" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A70" t="s">
+        <v>62</v>
+      </c>
+      <c r="B70" s="8">
+        <v>4.9305555555555554E-2</v>
+      </c>
+      <c r="C70">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A71" t="s">
+        <v>63</v>
+      </c>
+      <c r="B71" s="8">
+        <v>4.9305555555555554E-2</v>
+      </c>
+      <c r="C71">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A72" t="s">
+        <v>64</v>
+      </c>
+      <c r="B72" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C72">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A73" t="s">
+        <v>65</v>
+      </c>
+      <c r="B73" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C73">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A75" s="3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A76" s="4" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A77" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A78" t="s">
+        <v>30</v>
+      </c>
+      <c r="B78" s="8">
+        <v>8.0555555555555554E-3</v>
+      </c>
+      <c r="C78">
         <v>192</v>
       </c>
-      <c r="D67" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A68" t="s">
-        <v>91</v>
-      </c>
-      <c r="B68" s="8">
-        <v>1.494212962962963E-2</v>
-      </c>
-      <c r="C68">
-        <v>192</v>
-      </c>
-      <c r="D68" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A69" t="s">
-        <v>92</v>
-      </c>
-      <c r="B69" s="8">
-        <v>1.3530092592592592E-2</v>
-      </c>
-      <c r="C69">
-        <v>192</v>
-      </c>
-      <c r="D69" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A70" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A71" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A72" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A74" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A75" t="s">
-        <v>93</v>
-      </c>
-      <c r="B75" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="C75">
-        <v>1</v>
-      </c>
-      <c r="D75" t="s">
-        <v>96</v>
-      </c>
-      <c r="F75" s="6"/>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A76" t="s">
-        <v>94</v>
-      </c>
-      <c r="B76" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="C76">
-        <v>1</v>
-      </c>
-      <c r="D76" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A78" s="3" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B79" s="10"/>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A80" s="2" t="s">
-        <v>34</v>
+      <c r="D78" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A79" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A80" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>63</v>
-      </c>
-      <c r="B81" s="8">
-        <v>7.2453703703703708E-3</v>
-      </c>
-      <c r="C81">
-        <v>192</v>
-      </c>
-      <c r="D81" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>58</v>
+        <v>29</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A84" t="s">
-        <v>64</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="B83" s="8"/>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A85" t="s">
-        <v>62</v>
+      <c r="A85" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A86" t="s">
+        <v>33</v>
+      </c>
+      <c r="B86" s="8">
+        <v>4.340277777777778E-3</v>
+      </c>
+      <c r="C86">
+        <v>192</v>
+      </c>
+      <c r="D86" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A87" s="2" t="s">
-        <v>40</v>
+      <c r="A87" t="s">
+        <v>32</v>
+      </c>
+      <c r="B87" s="8">
+        <v>4.8958333333333336E-3</v>
+      </c>
+      <c r="C87">
+        <v>192</v>
+      </c>
+      <c r="D87" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>69</v>
-      </c>
-      <c r="B88" s="8">
-        <v>0.24607638888888889</v>
-      </c>
-      <c r="C88">
-        <v>1152</v>
-      </c>
-      <c r="D88" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>70</v>
-      </c>
-      <c r="B89" s="8">
-        <v>0.12196759259259259</v>
-      </c>
-      <c r="C89">
-        <f>6*192</f>
-        <v>1152</v>
-      </c>
-      <c r="D89" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A91" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A92" t="s">
-        <v>68</v>
+      <c r="A92" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A93" t="s">
+        <v>56</v>
+      </c>
+      <c r="B93" s="8">
+        <v>8.2638888888888887E-2</v>
+      </c>
+      <c r="C93">
+        <v>1</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A94" s="2" t="s">
-        <v>74</v>
+      <c r="A94" t="s">
+        <v>57</v>
+      </c>
+      <c r="B94" s="8">
+        <v>0.37013888888888891</v>
+      </c>
+      <c r="C94">
+        <v>1</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>86</v>
-      </c>
-      <c r="B95" s="9" t="s">
-        <v>97</v>
+        <v>58</v>
+      </c>
+      <c r="B95" s="8" t="s">
+        <v>38</v>
       </c>
       <c r="C95">
         <v>1</v>
-      </c>
-      <c r="D95" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>87</v>
-      </c>
-      <c r="B96" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="B96" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C96">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A98" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A99" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A100" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A102" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A103" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="C96">
-        <v>1</v>
-      </c>
-      <c r="D96" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A98" s="3" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A99" s="5" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A100" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A101" t="s">
-        <v>45</v>
-      </c>
-      <c r="B101" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="C101">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A102" t="s">
-        <v>46</v>
-      </c>
-      <c r="B102" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="C102">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A103" t="s">
-        <v>50</v>
-      </c>
-      <c r="B103" s="8">
-        <v>5.5555555555555558E-3</v>
-      </c>
-      <c r="C103">
-        <v>1</v>
-      </c>
+      <c r="B103" s="8"/>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
-        <v>51</v>
-      </c>
-      <c r="B104" s="11">
-        <v>6.2500000000000003E-3</v>
+        <v>6</v>
+      </c>
+      <c r="B104" s="8">
+        <v>7.7118055555555551E-2</v>
       </c>
       <c r="C104">
-        <v>1</v>
+        <v>192</v>
+      </c>
+      <c r="D104" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
-        <v>52</v>
-      </c>
-      <c r="B105" s="8">
-        <v>2.7777777777777779E-3</v>
-      </c>
-      <c r="C105">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="B105" s="8"/>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
-        <v>53</v>
-      </c>
-      <c r="B106" s="8">
-        <v>7.1527777777777773E-2</v>
-      </c>
-      <c r="C106">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
-        <v>54</v>
-      </c>
-      <c r="B107" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="C107">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
-        <v>47</v>
+        <v>1</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A111" s="2" t="s">
-        <v>40</v>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A110" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A112" t="s">
-        <v>56</v>
-      </c>
-      <c r="B112" s="8">
-        <v>6.134259259259259E-4</v>
-      </c>
-      <c r="C112">
-        <v>128</v>
-      </c>
-      <c r="D112" t="s">
-        <v>19</v>
+      <c r="A112" s="2" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
-        <v>57</v>
+        <v>9</v>
       </c>
       <c r="B113" s="8">
-        <v>1.0300925925925926E-3</v>
+        <v>0.15875</v>
       </c>
       <c r="C113">
-        <v>128</v>
+        <v>256</v>
       </c>
       <c r="D113" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
-        <v>80</v>
-      </c>
-      <c r="B114" s="8">
-        <v>1.3773148148148147E-3</v>
-      </c>
-      <c r="C114">
-        <v>128</v>
-      </c>
-      <c r="D114" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
-        <v>81</v>
-      </c>
-      <c r="B115" s="8">
-        <v>1.5509259259259259E-3</v>
-      </c>
-      <c r="C115">
-        <v>128</v>
-      </c>
-      <c r="D115" t="s">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
-        <v>44</v>
+        <v>2</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
-        <v>43</v>
+        <v>7</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A120" s="2" t="s">
-        <v>74</v>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A119" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A121" t="s">
-        <v>82</v>
-      </c>
-      <c r="B121" s="8">
-        <v>4.9305555555555554E-2</v>
-      </c>
-      <c r="C121">
-        <v>1</v>
+      <c r="A121" s="2" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
-        <v>83</v>
+        <v>20</v>
       </c>
       <c r="B122" s="8">
-        <v>4.9305555555555554E-2</v>
+        <v>4.6296296296296294E-3</v>
       </c>
       <c r="C122">
-        <v>1</v>
+        <v>192</v>
+      </c>
+      <c r="D122" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
-        <v>84</v>
-      </c>
-      <c r="B123" s="8" t="s">
-        <v>49</v>
+        <v>21</v>
+      </c>
+      <c r="B123" s="8">
+        <v>4.4791666666666669E-3</v>
       </c>
       <c r="C123">
-        <v>1</v>
+        <v>192</v>
+      </c>
+      <c r="D123" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
-        <v>85</v>
-      </c>
-      <c r="B124" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="C124">
-        <v>1</v>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A125" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A126" s="3" t="s">
-        <v>33</v>
+      <c r="A126" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A127" s="4" t="s">
-        <v>75</v>
+      <c r="A127" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A128" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A129" t="s">
-        <v>39</v>
-      </c>
-      <c r="B129" s="8">
-        <v>8.0555555555555554E-3</v>
-      </c>
-      <c r="C129">
-        <v>192</v>
-      </c>
-      <c r="D129" t="s">
-        <v>18</v>
+      <c r="A128" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A130" t="s">
-        <v>35</v>
+      <c r="A130" s="2" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
-        <v>36</v>
+        <v>18</v>
+      </c>
+      <c r="B131" s="8">
+        <v>3.1250000000000002E-3</v>
+      </c>
+      <c r="C131">
+        <v>192</v>
+      </c>
+      <c r="D131" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
-        <v>37</v>
+        <v>17</v>
+      </c>
+      <c r="B132" s="8">
+        <v>5.3969907407407404E-2</v>
+      </c>
+      <c r="C132">
+        <v>192</v>
+      </c>
+      <c r="D132" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
-        <v>38</v>
+        <v>16</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
-        <v>73</v>
-      </c>
-      <c r="B134" s="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A135" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A136" s="2" t="s">
-        <v>40</v>
+      <c r="A136" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
-        <v>42</v>
-      </c>
-      <c r="C137">
-        <v>192</v>
-      </c>
-      <c r="D137" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
-        <v>41</v>
-      </c>
-      <c r="B138" s="8">
-        <v>4.8958333333333336E-3</v>
-      </c>
-      <c r="C138">
-        <v>192</v>
-      </c>
-      <c r="D138" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A139" t="s">
-        <v>44</v>
+        <v>101</v>
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A140" t="s">
-        <v>43</v>
+      <c r="A140" s="2" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
-        <v>66</v>
+        <v>20</v>
+      </c>
+      <c r="B141" s="8">
+        <v>5.4282407407407404E-3</v>
+      </c>
+      <c r="C141">
+        <v>192</v>
+      </c>
+      <c r="D141" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A142" t="s">
+        <v>21</v>
+      </c>
+      <c r="B142" s="8">
+        <v>5.4166666666666669E-3</v>
+      </c>
+      <c r="C142">
+        <v>192</v>
+      </c>
+      <c r="D142" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A143" s="2" t="s">
-        <v>74</v>
+      <c r="A143" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A145" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A146" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A147" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A149" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A150" t="s">
+        <v>11</v>
+      </c>
+      <c r="B150" s="8">
+        <v>0.17752314814814815</v>
+      </c>
+      <c r="C150">
+        <v>256</v>
+      </c>
+      <c r="D150" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A151" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A152" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A153" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A154" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A155" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A156" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A158" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A159" t="s">
+        <v>20</v>
+      </c>
+      <c r="B159" s="8">
+        <v>5.4398148148148149E-3</v>
+      </c>
+      <c r="C159">
+        <v>192</v>
+      </c>
+      <c r="D159" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A160" t="s">
+        <v>21</v>
+      </c>
+      <c r="B160" s="8">
+        <v>5.4629629629629629E-3</v>
+      </c>
+      <c r="C160">
+        <v>192</v>
+      </c>
+      <c r="D160" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A161" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A162" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A163" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A164" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A165" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A167" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A168" t="s">
+        <v>89</v>
+      </c>
+      <c r="B168" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C168">
+        <v>1</v>
+      </c>
+      <c r="D168" t="s">
         <v>76</v>
       </c>
-      <c r="B144" s="8">
-        <v>8.2638888888888887E-2</v>
-      </c>
-      <c r="C144">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A145" t="s">
-        <v>77</v>
-      </c>
-      <c r="B145" s="8">
-        <v>0.37013888888888891</v>
-      </c>
-      <c r="C145">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A146" t="s">
-        <v>78</v>
-      </c>
-      <c r="B146" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="C146">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A147" t="s">
-        <v>79</v>
-      </c>
-      <c r="B147" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="C147">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A149" s="1" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A150" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A151" t="s">
-        <v>102</v>
+    </row>
+    <row r="169" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A169" t="s">
+        <v>90</v>
       </c>
     </row>
   </sheetData>

--- a/ComputationTimePerFile.xlsx
+++ b/ComputationTimePerFile.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ramon/Documents/GitHub/LSPS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F31B239E-6F8C-8247-AAA6-70C089ACF654}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DB424F1-079E-8B4A-ABD6-2B542AF698E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="840" yWindow="1000" windowWidth="25240" windowHeight="17440" xr2:uid="{6A15F2D7-94BC-F647-8DE7-DD7F3A5D979B}"/>
   </bookViews>
